--- a/EncordadosBruno/image/torneo_advanced_01KR42E3NRTHEKKH1VHSNZK74E_2026-05-19.xlsx
+++ b/EncordadosBruno/image/torneo_advanced_01KR42E3NRTHEKKH1VHSNZK74E_2026-05-19.xlsx
@@ -39,37 +39,22 @@
     <x:t>TournamentId</x:t>
   </x:si>
   <x:si>
-    <x:t>01KR424NQJ683QVB6F0P1B4XGM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>jugador_ana</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ana Pérez</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ana@tenis.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>967890123</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01KR42E3NRTHEKKH1VHSNZK74E</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01KR424NQJR7CEHQW4STCQ3GGE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>jugador_juan</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Juan Martínez</x:t>
-  </x:si>
-  <x:si>
-    <x:t>juan@tenis.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>956789012</x:t>
+    <x:t>01KS0Q28TED4PWJPT7DMJ46WBN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>jugador_pedro</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Pedro Rodríguez</x:t>
+  </x:si>
+  <x:si>
+    <x:t>pedro@tenis.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>978901234</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01KS0Q28TE9N7TG55K98TCB4X0</x:t>
   </x:si>
   <x:si>
     <x:t>Marca</x:t>
@@ -87,49 +72,55 @@
     <x:t>Type</x:t>
   </x:si>
   <x:si>
+    <x:t>Tourna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Lead Tape 1/2"</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LeadTape</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Wilson</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ShockShield</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Silicone</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Calibre</x:t>
+  </x:si>
+  <x:si>
+    <x:t>StringFormat</x:t>
+  </x:si>
+  <x:si>
+    <x:t>StringsType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Luxilon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALU Power</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Reel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Polyester</x:t>
+  </x:si>
+  <x:si>
     <x:t>Head</x:t>
   </x:si>
   <x:si>
-    <x:t>Hydrosorb Comfort</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Grip</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Babolat</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Pro Overgrip</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Overgrip</x:t>
-  </x:si>
-  <x:si>
-    <x:t>StringFormat</x:t>
-  </x:si>
-  <x:si>
-    <x:t>StringsType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RPM Blast</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Reel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Polyester</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Wilson</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Champion's Choice</x:t>
+    <x:t>Intellitour</x:t>
   </x:si>
   <x:si>
     <x:t>Set</x:t>
   </x:si>
   <x:si>
-    <x:t>NaturalGut</x:t>
+    <x:t>Multifilament</x:t>
   </x:si>
   <x:si>
     <x:t>Owner</x:t>
@@ -153,25 +144,25 @@
     <x:t>SupervisorList</x:t>
   </x:si>
   <x:si>
-    <x:t>01KR42E3NRTHEKKH1VHSNZK74D</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Torneo Madrileño 2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-05-12 06:29</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-05-26 06:29</x:t>
+    <x:t>01KS0Q28TE2EFVQTCW8EN0W0MF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Open Circuit Barcelona</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-06-09 19:44</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-06-23 19:44</x:t>
   </x:si>
   <x:si>
     <x:t>default-680x600_kw5ji6</x:t>
   </x:si>
   <x:si>
-    <x:t>01KR424NQJKSBKBMH15K4V835W;01KR424NQJKMNYS1FEC7NXBBH2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01KR424NQJKTASKFZ3M5NP7GHS</x:t>
+    <x:t>01KS0Q28TE7CMWS2D8RVDFA7YJ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01KS0Q28TEXTDY9TQNRAXKAJ81</x:t>
   </x:si>
   <x:si>
     <x:t>PlayerId</x:t>
@@ -192,52 +183,43 @@
     <x:t>PayStatus</x:t>
   </x:si>
   <x:si>
-    <x:t>01KR42ME5P1Q2BGWW1DY11Z4TJ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01KR424NQJKSBKBMH15K4V835W</x:t>
+    <x:t>01KR424NQJ6VBW36R0TS0HYGAR</x:t>
   </x:si>
   <x:si>
     <x:t>Máquina Alpha-1</x:t>
   </x:si>
   <x:si>
-    <x:t>Cliente preferente, ser cuidadoso con el logotipo</x:t>
+    <x:t>Revisar empuñadura, cambiar grip si es necesario</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01KR424NQJDA22KTM967R9RW9N</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01KS0Q28TE3RJTW6W35NJRMTZ4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CANCELADO: Cliente cambió de planes</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CANCELED</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01KSJY6RMWED3CSNSCJ2DFZ0NR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01KSJY6NH37SX8R4BMW6HHJNVE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Nuevo pedido para el Torneo Madrileño</x:t>
   </x:si>
   <x:si>
     <x:t>PENDING_PAYMENT</x:t>
   </x:si>
   <x:si>
-    <x:t>01KR424NQJVJRJR4GKWNTP2HK2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01KR424NQJKMNYS1FEC7NXBBH2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Máquina Beta-2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Tensión estándar, sin especificaciones especiales</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01KR424NQJWHMD2MN2YFQA7K6E</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Máquina Gamma-3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Segunda raqueta del jugador</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01KR42766T458MYAE94CSAYWY7</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Banco de trabajo</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Microfisura en el marco. Cliente prioritario</x:t>
+    <x:t>01KSJY6RQTP3YJ43E54RX6E8Z2</x:t>
   </x:si>
   <x:si>
     <x:t>PedidoId</x:t>
@@ -276,66 +258,51 @@
     <x:t>Status</x:t>
   </x:si>
   <x:si>
-    <x:t>01KR424NQJVJRJR4GKWNTP2HA2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Head Graphene 360</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-05-20 06:29</x:t>
+    <x:t>01KR424NQJ6VBW36R0TS0HYGA3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tecnifibre TF-X</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-06-05 19:44</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Azul</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mantenimiento</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COMPLETED</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01KR424NQJDA22KTM967R9RWAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Dunlop Biomimetic</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-06-15 19:44</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Amarillo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Wilson NPS Tour</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01KSJY6RMWAG9CHFHVPD45MYSS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Wilson Clash 100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-06-15 00:00</x:t>
   </x:si>
   <x:si>
     <x:t>Rojo</x:t>
   </x:si>
   <x:si>
-    <x:t>Luxilon Big Banger</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IN_PROGRESS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01KR424NQJWHMD2MN2YFQA7K7E</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Yonex Vcore Pro</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-05-21 06:29</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Blanco</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prince Synthetic Gut</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DELIVERED_TOpLAYER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01KR42766T458MYAE94CSAYWB8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Wilson Pro Staff</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-05-24 06:29</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Negro</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Reparación</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01KR42ME5P1Q2BGWW1DY11Z5AA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Wilson Pro H</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-05-22 06:29</x:t>
-  </x:si>
-  <x:si>
     <x:t>Babolat RPM Blast</x:t>
   </x:si>
   <x:si>
@@ -343,6 +310,9 @@
   </x:si>
   <x:si>
     <x:t>PENDING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01KSJY6RQTXJYMJN1F3SRA0WR7</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -713,15 +683,15 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:F3"/>
+  <x:dimension ref="A1:F2"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="32.139196" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="13.139196" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="13.710625" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="15.710625" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="32.567768" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="14.424911" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15.710625" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="16.996339" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="10.282054" style="0" customWidth="1"/>
-    <x:col min="6" max="6" width="30.853482" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="30.139196" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:6">
@@ -761,26 +731,6 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:6">
-      <x:c r="A3" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="B3" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C3" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D3" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E3" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="F3" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
     </x:row>
@@ -802,12 +752,12 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="2.710625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="30.853482" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="7.853482" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="18.567768" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="30.139196" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="7.424911" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="14.282054" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="5.710625" style="0" customWidth="1"/>
     <x:col min="6" max="6" width="6.282054" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="8.710625" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="9.424911" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:7">
@@ -818,65 +768,65 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F1" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G1" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:7">
       <x:c r="A2" s="0">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>100</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>8.99</x:v>
+        <x:v>12.99</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:7">
       <x:c r="A3" s="0">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>200</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>3.99</x:v>
+        <x:v>9.99</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -893,20 +843,21 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:H3"/>
+  <x:dimension ref="A1:I3"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="2.710625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="30.853482" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="7.853482" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="18.139196" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="30.139196" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="7.282054" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="10.424911" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="5.710625" style="0" customWidth="1"/>
     <x:col min="6" max="6" width="6.282054" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="12.853482" style="0" customWidth="1"/>
-    <x:col min="8" max="8" width="11.282054" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="6.853482" style="0" customWidth="1"/>
+    <x:col min="8" max="8" width="12.853482" style="0" customWidth="1"/>
+    <x:col min="9" max="9" width="13.139196" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:8">
+    <x:row r="1" spans="1:9">
       <x:c r="A1" s="1" t="s">
         <x:v>0</x:v>
       </x:c>
@@ -914,74 +865,83 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F1" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G1" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="H1" s="1" t="s">
-        <x:v>29</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:8">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="I1" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:9">
       <x:c r="A2" s="0">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>50</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>19.99</x:v>
-      </x:c>
-      <x:c r="G2" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>21.99</x:v>
+      </x:c>
+      <x:c r="G2" s="0">
+        <x:v>1.25</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:8">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="I2" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:9">
       <x:c r="A3" s="0">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D3" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E3" s="0">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="F3" s="0">
+        <x:v>18.5</x:v>
+      </x:c>
+      <x:c r="G3" s="0">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="H3" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="I3" s="0" t="s">
         <x:v>33</x:v>
-      </x:c>
-      <x:c r="D3" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="E3" s="0">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="F3" s="0">
-        <x:v>24.99</x:v>
-      </x:c>
-      <x:c r="G3" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="H3" s="0" t="s">
-        <x:v>36</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1001,14 +961,14 @@
   <x:dimension ref="A1:H2"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="30.853482" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="31.139196" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="21.710625" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="30.139196" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="32.853482" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="21.282054" style="0" customWidth="1"/>
     <x:col min="4" max="4" width="16.424911" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="15.710625" style="0" customWidth="1"/>
     <x:col min="6" max="6" width="21.710625" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="63.710625" style="0" customWidth="1"/>
-    <x:col min="8" max="8" width="31.424911" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="31.567768" style="0" customWidth="1"/>
+    <x:col min="8" max="8" width="30.567768" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:8">
@@ -1016,25 +976,25 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C1" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D1" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E1" s="1" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s">
+      <x:c r="F1" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="D1" s="1" t="s">
+      <x:c r="G1" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="E1" s="1" t="s">
+      <x:c r="H1" s="1" t="s">
         <x:v>40</x:v>
-      </x:c>
-      <x:c r="F1" s="1" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="G1" s="1" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="H1" s="1" t="s">
-        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:8">
@@ -1042,25 +1002,25 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C2" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D2" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="E2" s="0" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="C2" s="0" t="s">
+      <x:c r="F2" s="0" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="D2" s="0" t="s">
+      <x:c r="G2" s="0" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="E2" s="0" t="s">
+      <x:c r="H2" s="0" t="s">
         <x:v>47</x:v>
-      </x:c>
-      <x:c r="F2" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="G2" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="H2" s="0" t="s">
-        <x:v>50</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1080,13 +1040,13 @@
   <x:dimension ref="A1:H5"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="33.567768" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="30.853482" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="32.139196" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="31.996339" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="18.282054" style="0" customWidth="1"/>
-    <x:col min="6" max="6" width="44.424911" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="5.139196" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="31.996339" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="30.139196" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="32.567768" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="31.567768" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="16.139196" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="45.139196" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="5.567768" style="0" customWidth="1"/>
     <x:col min="8" max="8" width="19.139196" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -1098,126 +1058,126 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D1" s="1" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E1" s="1" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="F1" s="1" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="D1" s="1" t="s">
+      <x:c r="G1" s="1" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="E1" s="1" t="s">
+      <x:c r="H1" s="1" t="s">
         <x:v>53</x:v>
-      </x:c>
-      <x:c r="F1" s="1" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="G1" s="1" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="H1" s="1" t="s">
-        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:8">
       <x:c r="A2" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E2" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>45.5</x:v>
+        <x:v>52.75</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:8">
       <x:c r="A3" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>38</x:v>
+        <x:v>35.5</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:8">
       <x:c r="A4" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>40</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:8">
       <x:c r="A5" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>60</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="H5" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1237,19 +1197,20 @@
   <x:dimension ref="A1:N5"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="2" width="33.567768" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="18.567768" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="32.996339" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="31.996339" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="18.139196" style="0" customWidth="1"/>
     <x:col min="4" max="4" width="6.567768" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="15.710625" style="0" customWidth="1"/>
     <x:col min="6" max="6" width="9.282054" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="6.710625" style="0" customWidth="1"/>
-    <x:col min="8" max="8" width="19.139196" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="8.282054" style="0" customWidth="1"/>
+    <x:col min="8" max="8" width="17.567768" style="0" customWidth="1"/>
     <x:col min="9" max="9" width="9.139196" style="0" customWidth="1"/>
     <x:col min="10" max="10" width="10.710625" style="0" customWidth="1"/>
-    <x:col min="11" max="11" width="19.139196" style="0" customWidth="1"/>
+    <x:col min="11" max="11" width="15.710625" style="0" customWidth="1"/>
     <x:col min="12" max="12" width="9.282054" style="0" customWidth="1"/>
     <x:col min="13" max="13" width="10.853482" style="0" customWidth="1"/>
-    <x:col min="14" max="14" width="20.853482" style="0" customWidth="1"/>
+    <x:col min="14" max="14" width="11.996339" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:14">
@@ -1257,219 +1218,219 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="C1" s="1" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="D1" s="1" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="E1" s="1" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="F1" s="1" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="G1" s="1" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="H1" s="1" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="I1" s="1" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s">
+      <x:c r="J1" s="1" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="D1" s="1" t="s">
+      <x:c r="K1" s="1" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="E1" s="1" t="s">
+      <x:c r="L1" s="1" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="F1" s="1" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="G1" s="1" t="s">
+      <x:c r="M1" s="1" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="H1" s="1" t="s">
+      <x:c r="N1" s="1" t="s">
         <x:v>78</x:v>
-      </x:c>
-      <x:c r="I1" s="1" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="J1" s="1" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="K1" s="1" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="L1" s="1" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="M1" s="1" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="N1" s="1" t="s">
-        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:14">
       <x:c r="A2" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E2" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="F2" s="0" t="b">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>25</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J2" s="0">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K2" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="L2" s="0">
-        <x:v>24.5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="M2" s="0">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N2" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:14">
       <x:c r="A3" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D3" s="0">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="F3" s="0" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>24</x:v>
+        <x:v>23.5</x:v>
       </x:c>
       <x:c r="J3" s="0">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="L3" s="0">
-        <x:v>23.5</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="M3" s="0">
         <x:v>1</x:v>
       </x:c>
       <x:c r="N3" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:14">
       <x:c r="A4" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="F4" s="0" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>0</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="J4" s="0">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="L4" s="0">
-        <x:v>0</x:v>
+        <x:v>25.5</x:v>
       </x:c>
       <x:c r="M4" s="0">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="N4" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:14">
       <x:c r="A5" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="F5" s="0" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="H5" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>26.5</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="J5" s="0">
         <x:v>2</x:v>
       </x:c>
       <x:c r="K5" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="L5" s="0">
-        <x:v>25</x:v>
+        <x:v>25.5</x:v>
       </x:c>
       <x:c r="M5" s="0">
         <x:v>1</x:v>
       </x:c>
       <x:c r="N5" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
